--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/135.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/135.xlsx
@@ -426,13 +426,13 @@
         <v>-16.7034234809685</v>
       </c>
       <c r="E2">
-        <v>-23.24486293940989</v>
+        <v>-18.06715067020785</v>
       </c>
       <c r="F2">
-        <v>-5.633658099192513</v>
+        <v>-5.625609681506913</v>
       </c>
       <c r="G2">
-        <v>-14.04946976914098</v>
+        <v>-12.90249485105954</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.03194519576486</v>
       </c>
       <c r="E3">
-        <v>-22.75947392442374</v>
+        <v>-18.73049965674744</v>
       </c>
       <c r="F3">
-        <v>-5.558009102866654</v>
+        <v>-5.580325320698073</v>
       </c>
       <c r="G3">
-        <v>-15.29319869115315</v>
+        <v>-12.2398792297378</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.27416224388085</v>
       </c>
       <c r="E4">
-        <v>-23.38866915999747</v>
+        <v>-19.47797863340152</v>
       </c>
       <c r="F4">
-        <v>-5.644880820765641</v>
+        <v>-5.440576426376185</v>
       </c>
       <c r="G4">
-        <v>-14.51597032798907</v>
+        <v>-12.4207277114571</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.51312788009697</v>
       </c>
       <c r="E5">
-        <v>-24.37654670782274</v>
+        <v>-19.93818933290503</v>
       </c>
       <c r="F5">
-        <v>-5.883480453998399</v>
+        <v>-5.631813324986479</v>
       </c>
       <c r="G5">
-        <v>-14.436427850317</v>
+        <v>-11.71060576164682</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-13.73372692762827</v>
       </c>
       <c r="E6">
-        <v>-25.23822927047627</v>
+        <v>-20.16790523389212</v>
       </c>
       <c r="F6">
-        <v>-6.109243705957376</v>
+        <v>-5.489295198437032</v>
       </c>
       <c r="G6">
-        <v>-13.4398592924485</v>
+        <v>-11.67613636149193</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.93887124774236</v>
       </c>
       <c r="E7">
-        <v>-24.45850755888757</v>
+        <v>-20.69561283847996</v>
       </c>
       <c r="F7">
-        <v>-6.222170063776616</v>
+        <v>-5.780024820695366</v>
       </c>
       <c r="G7">
-        <v>-14.08750959265998</v>
+        <v>-11.2992473045736</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.12276195182859</v>
       </c>
       <c r="E8">
-        <v>-25.13893794938409</v>
+        <v>-21.79028538882812</v>
       </c>
       <c r="F8">
-        <v>-6.349958161169482</v>
+        <v>-5.53757907761141</v>
       </c>
       <c r="G8">
-        <v>-13.30810289053105</v>
+        <v>-10.26051729398971</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.28871473977319</v>
       </c>
       <c r="E9">
-        <v>-25.05793713480889</v>
+        <v>-21.07293887822107</v>
       </c>
       <c r="F9">
-        <v>-6.494406383767451</v>
+        <v>-5.694719545555073</v>
       </c>
       <c r="G9">
-        <v>-13.17342327690242</v>
+        <v>-10.79704747790278</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.42276430401201</v>
       </c>
       <c r="E10">
-        <v>-25.98276926749937</v>
+        <v>-22.62332082490912</v>
       </c>
       <c r="F10">
-        <v>-6.393938257502615</v>
+        <v>-5.754697487354771</v>
       </c>
       <c r="G10">
-        <v>-12.73520967441463</v>
+        <v>-9.990598584536315</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.541758438640976</v>
       </c>
       <c r="E11">
-        <v>-27.26960761236303</v>
+        <v>-23.20445989431346</v>
       </c>
       <c r="F11">
-        <v>-6.418222676283085</v>
+        <v>-5.680051643953703</v>
       </c>
       <c r="G11">
-        <v>-11.91698848111052</v>
+        <v>-9.624859444994252</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.674416431449133</v>
       </c>
       <c r="E12">
-        <v>-29.0837867554199</v>
+        <v>-22.91511304759336</v>
       </c>
       <c r="F12">
-        <v>-6.179959774399564</v>
+        <v>-5.794507996365913</v>
       </c>
       <c r="G12">
-        <v>-11.12539731612431</v>
+        <v>-9.685157721446537</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.851012057256285</v>
       </c>
       <c r="E13">
-        <v>-29.74145250707986</v>
+        <v>-23.73058253299861</v>
       </c>
       <c r="F13">
-        <v>-6.142682412906184</v>
+        <v>-5.724848096362294</v>
       </c>
       <c r="G13">
-        <v>-9.76944752142192</v>
+        <v>-9.004420173842821</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.124784236460129</v>
       </c>
       <c r="E14">
-        <v>-27.78171915246845</v>
+        <v>-24.82754649119465</v>
       </c>
       <c r="F14">
-        <v>-6.707457509563067</v>
+        <v>-5.605400830348216</v>
       </c>
       <c r="G14">
-        <v>-10.28487959861321</v>
+        <v>-8.71012591758377</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.551444481919089</v>
       </c>
       <c r="E15">
-        <v>-30.61483211809519</v>
+        <v>-25.38705756873835</v>
       </c>
       <c r="F15">
-        <v>-6.130051466748297</v>
+        <v>-5.319654666385124</v>
       </c>
       <c r="G15">
-        <v>-9.901852790265073</v>
+        <v>-8.33033682277304</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.167614532329383</v>
       </c>
       <c r="E16">
-        <v>-31.13855466555628</v>
+        <v>-26.23494639956451</v>
       </c>
       <c r="F16">
-        <v>-6.334106108365809</v>
+        <v>-5.27845250013728</v>
       </c>
       <c r="G16">
-        <v>-8.829484326456653</v>
+        <v>-7.741132548784632</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.011151883042738</v>
       </c>
       <c r="E17">
-        <v>-31.74247195921919</v>
+        <v>-26.4674925968064</v>
       </c>
       <c r="F17">
-        <v>-6.328556046767052</v>
+        <v>-5.051382084416685</v>
       </c>
       <c r="G17">
-        <v>-8.692338356401265</v>
+        <v>-7.686104660830867</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.103824140707938</v>
       </c>
       <c r="E18">
-        <v>-31.02572773565517</v>
+        <v>-27.68373203189048</v>
       </c>
       <c r="F18">
-        <v>-6.396644947991262</v>
+        <v>-4.80857020294069</v>
       </c>
       <c r="G18">
-        <v>-8.868303783450147</v>
+        <v>-7.552957829786918</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.43433063760691</v>
       </c>
       <c r="E19">
-        <v>-31.4925658568689</v>
+        <v>-27.87246071463414</v>
       </c>
       <c r="F19">
-        <v>-5.615458867353008</v>
+        <v>-4.774171418172038</v>
       </c>
       <c r="G19">
-        <v>-8.512373790340945</v>
+        <v>-7.464894007896766</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.985748880290095</v>
       </c>
       <c r="E20">
-        <v>-31.19628365220606</v>
+        <v>-28.43679914547003</v>
       </c>
       <c r="F20">
-        <v>-5.727503842255669</v>
+        <v>-4.648692809098177</v>
       </c>
       <c r="G20">
-        <v>-8.590393417064949</v>
+        <v>-7.293851362064781</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.728671389957841</v>
       </c>
       <c r="E21">
-        <v>-32.79508630722112</v>
+        <v>-29.26165615749317</v>
       </c>
       <c r="F21">
-        <v>-5.698627782961482</v>
+        <v>-4.195261060153785</v>
       </c>
       <c r="G21">
-        <v>-8.99261476844978</v>
+        <v>-7.625508435280047</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.609592113982711</v>
       </c>
       <c r="E22">
-        <v>-32.90158922317052</v>
+        <v>-29.47400762489785</v>
       </c>
       <c r="F22">
-        <v>-5.527086976087551</v>
+        <v>-4.306172828449416</v>
       </c>
       <c r="G22">
-        <v>-8.405810639977345</v>
+        <v>-8.165779535652486</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.576260774807508</v>
       </c>
       <c r="E23">
-        <v>-33.93076645394574</v>
+        <v>-28.84907141912834</v>
       </c>
       <c r="F23">
-        <v>-5.275811664857154</v>
+        <v>-3.776463352320438</v>
       </c>
       <c r="G23">
-        <v>-8.485290217284167</v>
+        <v>-7.651711403223378</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.57274529280665</v>
       </c>
       <c r="E24">
-        <v>-35.19649531722264</v>
+        <v>-29.96407228929693</v>
       </c>
       <c r="F24">
-        <v>-5.476146522652395</v>
+        <v>-3.884492402054327</v>
       </c>
       <c r="G24">
-        <v>-8.669541939817844</v>
+        <v>-8.093053471245778</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.53227885244951</v>
       </c>
       <c r="E25">
-        <v>-33.59558465755701</v>
+        <v>-30.18307608501888</v>
       </c>
       <c r="F25">
-        <v>-4.643174225460728</v>
+        <v>-3.838716819375627</v>
       </c>
       <c r="G25">
-        <v>-10.49712529422696</v>
+        <v>-8.324063338976121</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-12.40123307731966</v>
       </c>
       <c r="E26">
-        <v>-34.29956084865641</v>
+        <v>-30.01670221421407</v>
       </c>
       <c r="F26">
-        <v>-5.166633669535583</v>
+        <v>-3.586464862977329</v>
       </c>
       <c r="G26">
-        <v>-8.643971286072514</v>
+        <v>-8.437432970968462</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.13670256646862</v>
       </c>
       <c r="E27">
-        <v>-34.58607739912171</v>
+        <v>-29.90759542571027</v>
       </c>
       <c r="F27">
-        <v>-5.271454452318429</v>
+        <v>-3.340144017183077</v>
       </c>
       <c r="G27">
-        <v>-10.0744249081362</v>
+        <v>-8.542787772210229</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.69908128353142</v>
       </c>
       <c r="E28">
-        <v>-33.2458302318116</v>
+        <v>-29.27360227192541</v>
       </c>
       <c r="F28">
-        <v>-5.07043950488549</v>
+        <v>-3.661909252554697</v>
       </c>
       <c r="G28">
-        <v>-10.81581827111044</v>
+        <v>-8.609402569551444</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.07486729230885</v>
       </c>
       <c r="E29">
-        <v>-33.67400877042184</v>
+        <v>-29.57465748819234</v>
       </c>
       <c r="F29">
-        <v>-5.083936923346705</v>
+        <v>-3.591920490692167</v>
       </c>
       <c r="G29">
-        <v>-9.593674106014317</v>
+        <v>-8.365551095674267</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.27312900660433</v>
       </c>
       <c r="E30">
-        <v>-34.33805740619562</v>
+        <v>-30.44819106732393</v>
       </c>
       <c r="F30">
-        <v>-4.698570467155542</v>
+        <v>-3.60933194513161</v>
       </c>
       <c r="G30">
-        <v>-10.84885089450129</v>
+        <v>-8.625286567048867</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.31209440413455</v>
       </c>
       <c r="E31">
-        <v>-33.1488937172034</v>
+        <v>-29.36839681832797</v>
       </c>
       <c r="F31">
-        <v>-4.727243576436043</v>
+        <v>-3.473753880682818</v>
       </c>
       <c r="G31">
-        <v>-9.008548424130293</v>
+        <v>-8.80696599569853</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.23382729215304</v>
       </c>
       <c r="E32">
-        <v>-32.12627598102829</v>
+        <v>-29.34496649381229</v>
       </c>
       <c r="F32">
-        <v>-4.628788797143711</v>
+        <v>-3.514372876279091</v>
       </c>
       <c r="G32">
-        <v>-10.51998461117563</v>
+        <v>-9.280867279099661</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.08932545056888</v>
       </c>
       <c r="E33">
-        <v>-32.41691797131458</v>
+        <v>-29.3900791518767</v>
       </c>
       <c r="F33">
-        <v>-5.360010241147307</v>
+        <v>-3.606462480448313</v>
       </c>
       <c r="G33">
-        <v>-9.295685280933439</v>
+        <v>-8.572778004250486</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-13.91758204797952</v>
       </c>
       <c r="E34">
-        <v>-33.55013462817902</v>
+        <v>-28.25799687775117</v>
       </c>
       <c r="F34">
-        <v>-4.968766518233282</v>
+        <v>-3.669488814290313</v>
       </c>
       <c r="G34">
-        <v>-9.316730418926586</v>
+        <v>-8.646566753775302</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.76186075168606</v>
       </c>
       <c r="E35">
-        <v>-30.95340574151567</v>
+        <v>-29.36411741039072</v>
       </c>
       <c r="F35">
-        <v>-4.475635261509722</v>
+        <v>-3.622124422933043</v>
       </c>
       <c r="G35">
-        <v>-10.32622500185317</v>
+        <v>-8.245931153703781</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.65325395846648</v>
       </c>
       <c r="E36">
-        <v>-32.02398228166902</v>
+        <v>-27.2315684306986</v>
       </c>
       <c r="F36">
-        <v>-4.581000281676208</v>
+        <v>-3.625833852162779</v>
       </c>
       <c r="G36">
-        <v>-9.941887217471479</v>
+        <v>-8.310301401169371</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.59826110217843</v>
       </c>
       <c r="E37">
-        <v>-31.06126493543036</v>
+        <v>-27.55599736555612</v>
       </c>
       <c r="F37">
-        <v>-4.898230205517501</v>
+        <v>-3.396195497493506</v>
       </c>
       <c r="G37">
-        <v>-10.05702468078179</v>
+        <v>-8.623965659378698</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.60448427538309</v>
       </c>
       <c r="E38">
-        <v>-31.01276950728222</v>
+        <v>-27.39144167706539</v>
       </c>
       <c r="F38">
-        <v>-4.978726807884542</v>
+        <v>-3.427902916570462</v>
       </c>
       <c r="G38">
-        <v>-10.88893497989079</v>
+        <v>-8.560224415565569</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.66516883772994</v>
       </c>
       <c r="E39">
-        <v>-30.30676455982739</v>
+        <v>-27.13707729205455</v>
       </c>
       <c r="F39">
-        <v>-4.618029961316151</v>
+        <v>-3.66831336094574</v>
       </c>
       <c r="G39">
-        <v>-9.928598687676844</v>
+        <v>-7.628067486981903</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.7532100443186</v>
       </c>
       <c r="E40">
-        <v>-28.91065413715864</v>
+        <v>-26.2101394189505</v>
       </c>
       <c r="F40">
-        <v>-4.756484945754866</v>
+        <v>-3.511488500982544</v>
       </c>
       <c r="G40">
-        <v>-10.39617682909797</v>
+        <v>-8.792240689139852</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-13.85173147563381</v>
       </c>
       <c r="E41">
-        <v>-28.83785438901134</v>
+        <v>-26.29474942730981</v>
       </c>
       <c r="F41">
-        <v>-4.362327026317791</v>
+        <v>-3.61734474301889</v>
       </c>
       <c r="G41">
-        <v>-9.95855250371617</v>
+        <v>-7.284297127638444</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-13.93869687714419</v>
       </c>
       <c r="E42">
-        <v>-30.03302283453772</v>
+        <v>-25.86996950844231</v>
       </c>
       <c r="F42">
-        <v>-4.502347625147798</v>
+        <v>-3.506102456129541</v>
       </c>
       <c r="G42">
-        <v>-8.357963325298257</v>
+        <v>-7.535471528248489</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-13.98630060856913</v>
       </c>
       <c r="E43">
-        <v>-29.49694887422071</v>
+        <v>-25.08850433436066</v>
       </c>
       <c r="F43">
-        <v>-5.078712410137249</v>
+        <v>-3.507838714205809</v>
       </c>
       <c r="G43">
-        <v>-10.5136846430144</v>
+        <v>-7.688001603424869</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-13.99072251606912</v>
       </c>
       <c r="E44">
-        <v>-30.40657212695644</v>
+        <v>-25.33937273743759</v>
       </c>
       <c r="F44">
-        <v>-5.077447493113174</v>
+        <v>-3.408613553228873</v>
       </c>
       <c r="G44">
-        <v>-9.797534189777098</v>
+        <v>-7.936663299970607</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-13.95267896934044</v>
       </c>
       <c r="E45">
-        <v>-27.21528856664102</v>
+        <v>-24.41675502853685</v>
       </c>
       <c r="F45">
-        <v>-4.521733907475515</v>
+        <v>-3.629007327682904</v>
       </c>
       <c r="G45">
-        <v>-9.710076197720632</v>
+        <v>-7.566766115231219</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.87193210945585</v>
       </c>
       <c r="E46">
-        <v>-26.54743827693781</v>
+        <v>-23.77148371023588</v>
       </c>
       <c r="F46">
-        <v>-4.760411407244136</v>
+        <v>-3.727190402467118</v>
       </c>
       <c r="G46">
-        <v>-8.955592937684111</v>
+        <v>-7.748332985332548</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.76712024283491</v>
       </c>
       <c r="E47">
-        <v>-26.36725935312063</v>
+        <v>-23.52145760332439</v>
       </c>
       <c r="F47">
-        <v>-4.532112522665189</v>
+        <v>-3.61168119508595</v>
       </c>
       <c r="G47">
-        <v>-9.321921354332163</v>
+        <v>-7.812249688059256</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.65203752473155</v>
       </c>
       <c r="E48">
-        <v>-26.52420267680446</v>
+        <v>-23.42447580397612</v>
       </c>
       <c r="F48">
-        <v>-4.504053233630161</v>
+        <v>-3.533465916546217</v>
       </c>
       <c r="G48">
-        <v>-10.22726617459327</v>
+        <v>-8.207118317801367</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.53099455838978</v>
       </c>
       <c r="E49">
-        <v>-26.14560413586718</v>
+        <v>-22.99806110599186</v>
       </c>
       <c r="F49">
-        <v>-4.868611100663002</v>
+        <v>-3.536555726958659</v>
       </c>
       <c r="G49">
-        <v>-9.321315524498477</v>
+        <v>-7.792538699918436</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.42008649717321</v>
       </c>
       <c r="E50">
-        <v>-25.31175810293881</v>
+        <v>-22.54358345458206</v>
       </c>
       <c r="F50">
-        <v>-4.534097290962297</v>
+        <v>-3.784006465890331</v>
       </c>
       <c r="G50">
-        <v>-9.7791739042163</v>
+        <v>-7.816275311435009</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.32448324124631</v>
       </c>
       <c r="E51">
-        <v>-25.29207735490148</v>
+        <v>-21.75644863104281</v>
       </c>
       <c r="F51">
-        <v>-4.802245617820317</v>
+        <v>-3.792692726476086</v>
       </c>
       <c r="G51">
-        <v>-9.785857895660088</v>
+        <v>-7.954325060422618</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.23710681050626</v>
       </c>
       <c r="E52">
-        <v>-24.7057169549663</v>
+        <v>-21.49136534805581</v>
       </c>
       <c r="F52">
-        <v>-3.974330503622739</v>
+        <v>-3.637326621509219</v>
       </c>
       <c r="G52">
-        <v>-8.855442314030078</v>
+        <v>-8.508742121884364</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.16087631818279</v>
       </c>
       <c r="E53">
-        <v>-24.80520300044081</v>
+        <v>-21.588301862664</v>
       </c>
       <c r="F53">
-        <v>-4.849378894672205</v>
+        <v>-3.947724171012222</v>
       </c>
       <c r="G53">
-        <v>-10.68564099941522</v>
+        <v>-7.93337592825011</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.08752958695226</v>
       </c>
       <c r="E54">
-        <v>-23.76752129547917</v>
+        <v>-20.56113527434818</v>
       </c>
       <c r="F54">
-        <v>-4.590757621313784</v>
+        <v>-3.588353540655713</v>
       </c>
       <c r="G54">
-        <v>-9.752017499157658</v>
+        <v>-8.26124573736845</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.0010347768102</v>
       </c>
       <c r="E55">
-        <v>-23.38702985240669</v>
+        <v>-20.87453737499702</v>
       </c>
       <c r="F55">
-        <v>-4.652104854430309</v>
+        <v>-3.669621353074761</v>
       </c>
       <c r="G55">
-        <v>-10.59455795999325</v>
+        <v>-8.596468268129511</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.89913919629619</v>
       </c>
       <c r="E56">
-        <v>-23.00342281921694</v>
+        <v>-20.68151569889408</v>
       </c>
       <c r="F56">
-        <v>-4.142820433352159</v>
+        <v>-3.752577378260714</v>
       </c>
       <c r="G56">
-        <v>-10.14436349319884</v>
+        <v>-8.29081553012522</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.77281712432245</v>
       </c>
       <c r="E57">
-        <v>-24.40459607582626</v>
+        <v>-20.76421921969616</v>
       </c>
       <c r="F57">
-        <v>-4.515942790962543</v>
+        <v>-3.792382088700037</v>
       </c>
       <c r="G57">
-        <v>-10.12190475226043</v>
+        <v>-8.246371456260505</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.61064934011984</v>
       </c>
       <c r="E58">
-        <v>-22.0381197143199</v>
+        <v>-20.08723952639349</v>
       </c>
       <c r="F58">
-        <v>-4.692713909617749</v>
+        <v>-3.664868180917497</v>
       </c>
       <c r="G58">
-        <v>-10.87357073804303</v>
+        <v>-8.466645224806992</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.41687906343095</v>
       </c>
       <c r="E59">
-        <v>-22.00317348040271</v>
+        <v>-19.34466488708971</v>
       </c>
       <c r="F59">
-        <v>-4.422503776294161</v>
+        <v>-3.761067315772006</v>
       </c>
       <c r="G59">
-        <v>-11.60552573568481</v>
+        <v>-9.025720223842491</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.19001736871563</v>
       </c>
       <c r="E60">
-        <v>-23.34722003740526</v>
+        <v>-19.68309586357895</v>
       </c>
       <c r="F60">
-        <v>-4.934664288994831</v>
+        <v>-3.496138853008669</v>
       </c>
       <c r="G60">
-        <v>-11.0955461269967</v>
+        <v>-9.405357033558415</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.92737042405264</v>
       </c>
       <c r="E61">
-        <v>-21.83135411960368</v>
+        <v>-19.72403326860829</v>
       </c>
       <c r="F61">
-        <v>-4.837015511185423</v>
+        <v>-3.931275279494832</v>
       </c>
       <c r="G61">
-        <v>-10.61568586162488</v>
+        <v>-9.342311004308534</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.63882262538178</v>
       </c>
       <c r="E62">
-        <v>-22.31260410934683</v>
+        <v>-18.71382581545119</v>
       </c>
       <c r="F62">
-        <v>-4.466628422739083</v>
+        <v>-3.858000384145396</v>
       </c>
       <c r="G62">
-        <v>-11.23403948908657</v>
+        <v>-9.375648197888996</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.32588203055439</v>
       </c>
       <c r="E63">
-        <v>-22.38995497387184</v>
+        <v>-19.51989418881652</v>
       </c>
       <c r="F63">
-        <v>-4.464391002384121</v>
+        <v>-4.158998448728833</v>
       </c>
       <c r="G63">
-        <v>-11.26841288342083</v>
+        <v>-9.404784309180121</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.98832936772429</v>
       </c>
       <c r="E64">
-        <v>-22.72320990457031</v>
+        <v>-19.44207689146871</v>
       </c>
       <c r="F64">
-        <v>-4.424517537450367</v>
+        <v>-3.595415372764578</v>
       </c>
       <c r="G64">
-        <v>-11.40396979161736</v>
+        <v>-9.380610705652362</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.63807882488049</v>
       </c>
       <c r="E65">
-        <v>-20.98548498818494</v>
+        <v>-17.88425466198606</v>
       </c>
       <c r="F65">
-        <v>-4.630896992183836</v>
+        <v>-4.034499798292484</v>
       </c>
       <c r="G65">
-        <v>-11.99115132228128</v>
+        <v>-9.74887579144089</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.27888406052749</v>
       </c>
       <c r="E66">
-        <v>-21.88098619472775</v>
+        <v>-18.23619407644018</v>
       </c>
       <c r="F66">
-        <v>-4.780873738828089</v>
+        <v>-3.759881093651198</v>
       </c>
       <c r="G66">
-        <v>-10.91397594634983</v>
+        <v>-9.48664747927522</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.913295669064778</v>
       </c>
       <c r="E67">
-        <v>-22.52460009154191</v>
+        <v>-18.5624525147968</v>
       </c>
       <c r="F67">
-        <v>-4.809768022205139</v>
+        <v>-3.915537955576447</v>
       </c>
       <c r="G67">
-        <v>-11.3975241594524</v>
+        <v>-9.643117103643332</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.554939004173519</v>
       </c>
       <c r="E68">
-        <v>-21.98709739767548</v>
+        <v>-18.00146062625258</v>
       </c>
       <c r="F68">
-        <v>-4.604496094689213</v>
+        <v>-3.884578552264219</v>
       </c>
       <c r="G68">
-        <v>-11.50124024065223</v>
+        <v>-9.728327235278634</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.209551173679406</v>
       </c>
       <c r="E69">
-        <v>-20.81279163190244</v>
+        <v>-18.72867015324834</v>
       </c>
       <c r="F69">
-        <v>-4.408934289868903</v>
+        <v>-3.860439926146641</v>
       </c>
       <c r="G69">
-        <v>-11.22302530407742</v>
+        <v>-9.621062249260708</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.882348286131016</v>
       </c>
       <c r="E70">
-        <v>-21.33451259385213</v>
+        <v>-17.78864046178811</v>
       </c>
       <c r="F70">
-        <v>-4.520968495995327</v>
+        <v>-3.969979918023236</v>
       </c>
       <c r="G70">
-        <v>-10.94152299578211</v>
+        <v>-9.560383260071406</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.587814099452283</v>
       </c>
       <c r="E71">
-        <v>-20.67728157569691</v>
+        <v>-18.25084368985499</v>
       </c>
       <c r="F71">
-        <v>-4.982862846326721</v>
+        <v>-3.923930974101612</v>
       </c>
       <c r="G71">
-        <v>-11.46418530443117</v>
+        <v>-9.442872135609436</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.330414111355687</v>
       </c>
       <c r="E72">
-        <v>-21.74503687654348</v>
+        <v>-18.39893837532783</v>
       </c>
       <c r="F72">
-        <v>-4.745941485452034</v>
+        <v>-4.053535681208817</v>
       </c>
       <c r="G72">
-        <v>-11.75616217881273</v>
+        <v>-9.80906150934484</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.112614677977549</v>
       </c>
       <c r="E73">
-        <v>-20.9553525221379</v>
+        <v>-19.03154808030335</v>
       </c>
       <c r="F73">
-        <v>-5.018955642434098</v>
+        <v>-4.264323707259985</v>
       </c>
       <c r="G73">
-        <v>-12.05771315089386</v>
+        <v>-9.58231231372354</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.945008247962659</v>
       </c>
       <c r="E74">
-        <v>-19.83696888188558</v>
+        <v>-18.44079053210672</v>
       </c>
       <c r="F74">
-        <v>-5.08325186350459</v>
+        <v>-4.288806105849724</v>
       </c>
       <c r="G74">
-        <v>-11.74690589348493</v>
+        <v>-9.891739073642599</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.826966445316303</v>
       </c>
       <c r="E75">
-        <v>-21.32273403295818</v>
+        <v>-18.73457981182835</v>
       </c>
       <c r="F75">
-        <v>-4.761099780555862</v>
+        <v>-4.100931550527394</v>
       </c>
       <c r="G75">
-        <v>-10.84732473300769</v>
+        <v>-9.661179440105597</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.754579512491539</v>
       </c>
       <c r="E76">
-        <v>-22.46842437147675</v>
+        <v>-19.13044542415686</v>
       </c>
       <c r="F76">
-        <v>-5.21539965853839</v>
+        <v>-4.103958405017223</v>
       </c>
       <c r="G76">
-        <v>-11.25130398407387</v>
+        <v>-9.093026925201414</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.731080952187763</v>
       </c>
       <c r="E77">
-        <v>-22.64843574175566</v>
+        <v>-19.68727564508803</v>
       </c>
       <c r="F77">
-        <v>-5.298732590892617</v>
+        <v>-4.37932595379064</v>
       </c>
       <c r="G77">
-        <v>-11.48859395669221</v>
+        <v>-9.319832400096884</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.749108550479598</v>
       </c>
       <c r="E78">
-        <v>-23.32923746712081</v>
+        <v>-19.97895918439608</v>
       </c>
       <c r="F78">
-        <v>-4.773462335675242</v>
+        <v>-4.363991216430016</v>
       </c>
       <c r="G78">
-        <v>-10.42928228449068</v>
+        <v>-8.917094603607925</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.799737946487552</v>
       </c>
       <c r="E79">
-        <v>-23.72100028199837</v>
+        <v>-20.04665534233675</v>
       </c>
       <c r="F79">
-        <v>-4.916139508766026</v>
+        <v>-4.549934018969018</v>
       </c>
       <c r="G79">
-        <v>-11.06057683446538</v>
+        <v>-9.502925431691816</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.882422040268464</v>
       </c>
       <c r="E80">
-        <v>-23.11596445525556</v>
+        <v>-20.99673371762</v>
       </c>
       <c r="F80">
-        <v>-5.4221170871722</v>
+        <v>-4.436318459470649</v>
       </c>
       <c r="G80">
-        <v>-10.06002734558591</v>
+        <v>-9.4309574822136</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.98733708682659</v>
       </c>
       <c r="E81">
-        <v>-24.30539985268824</v>
+        <v>-21.38807538441485</v>
       </c>
       <c r="F81">
-        <v>-5.15049458742684</v>
+        <v>-4.880438530440173</v>
       </c>
       <c r="G81">
-        <v>-12.12901237017314</v>
+        <v>-9.631848006627653</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.104087726107025</v>
       </c>
       <c r="E82">
-        <v>-23.71589216331773</v>
+        <v>-21.71055707544907</v>
       </c>
       <c r="F82">
-        <v>-5.516714987837099</v>
+        <v>-4.667993769583406</v>
       </c>
       <c r="G82">
-        <v>-11.19310459349349</v>
+        <v>-8.919067688749331</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.23248925438411</v>
       </c>
       <c r="E83">
-        <v>-25.67370997342389</v>
+        <v>-22.10430336194201</v>
       </c>
       <c r="F83">
-        <v>-5.233341268115624</v>
+        <v>-4.625602896112544</v>
       </c>
       <c r="G83">
-        <v>-11.58225260054373</v>
+        <v>-9.487769754213032</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.365616848203782</v>
       </c>
       <c r="E84">
-        <v>-26.46703069245762</v>
+        <v>-23.30217077797696</v>
       </c>
       <c r="F84">
-        <v>-5.882794565788881</v>
+        <v>-4.809311591766196</v>
       </c>
       <c r="G84">
-        <v>-12.16349170196465</v>
+        <v>-8.847510246917984</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.499221283950934</v>
       </c>
       <c r="E85">
-        <v>-26.48149010996411</v>
+        <v>-24.05930898968941</v>
       </c>
       <c r="F85">
-        <v>-5.415771792866757</v>
+        <v>-4.672526596011525</v>
       </c>
       <c r="G85">
-        <v>-10.81841373881323</v>
+        <v>-8.619324274532639</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.642940949372752</v>
       </c>
       <c r="E86">
-        <v>-27.18996986846414</v>
+        <v>-25.20242262649762</v>
       </c>
       <c r="F86">
-        <v>-5.655894793753263</v>
+        <v>-4.781202600687001</v>
       </c>
       <c r="G86">
-        <v>-10.04953622677196</v>
+        <v>-8.980302849589231</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.799370985509015</v>
       </c>
       <c r="E87">
-        <v>-27.99756433757005</v>
+        <v>-26.2149848861387</v>
       </c>
       <c r="F87">
-        <v>-6.269509189928101</v>
+        <v>-4.928864060440429</v>
       </c>
       <c r="G87">
-        <v>-11.49461914957369</v>
+        <v>-8.109059958928153</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.971526718806713</v>
       </c>
       <c r="E88">
-        <v>-27.90397436525353</v>
+        <v>-27.13119933279259</v>
       </c>
       <c r="F88">
-        <v>-6.183045442974993</v>
+        <v>-5.136697299965811</v>
       </c>
       <c r="G88">
-        <v>-11.72562901730403</v>
+        <v>-9.148935418268627</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.174187177557785</v>
       </c>
       <c r="E89">
-        <v>-30.11764869255606</v>
+        <v>-28.24241892716478</v>
       </c>
       <c r="F89">
-        <v>-5.898388582146582</v>
+        <v>-5.170038259561089</v>
       </c>
       <c r="G89">
-        <v>-11.27696071200322</v>
+        <v>-9.040620989314752</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.410106612338383</v>
       </c>
       <c r="E90">
-        <v>-31.12440771275631</v>
+        <v>-29.58624132470396</v>
       </c>
       <c r="F90">
-        <v>-5.926523252615264</v>
+        <v>-5.14529575360687</v>
       </c>
       <c r="G90">
-        <v>-11.1315416886452</v>
+        <v>-8.867777406709402</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.678828417128635</v>
       </c>
       <c r="E91">
-        <v>-31.68155945534202</v>
+        <v>-31.4423247019908</v>
       </c>
       <c r="F91">
-        <v>-6.037626373780943</v>
+        <v>-5.405633404223893</v>
       </c>
       <c r="G91">
-        <v>-11.14392643950761</v>
+        <v>-7.759254475066603</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.9888001036513</v>
       </c>
       <c r="E92">
-        <v>-33.87675760869326</v>
+        <v>-32.78998045277747</v>
       </c>
       <c r="F92">
-        <v>-6.110875589740892</v>
+        <v>-5.334098908787739</v>
       </c>
       <c r="G92">
-        <v>-11.45822632246048</v>
+        <v>-8.520636912006966</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.332602326515</v>
       </c>
       <c r="E93">
-        <v>-35.16367067337804</v>
+        <v>-34.44518978003207</v>
       </c>
       <c r="F93">
-        <v>-6.587076673486035</v>
+        <v>-5.758217220449266</v>
       </c>
       <c r="G93">
-        <v>-10.9468331108271</v>
+        <v>-8.813315622042852</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.69944576287396</v>
       </c>
       <c r="E94">
-        <v>-36.96759282280754</v>
+        <v>-36.22056216508021</v>
       </c>
       <c r="F94">
-        <v>-6.280385239743157</v>
+        <v>-5.539205991190508</v>
       </c>
       <c r="G94">
-        <v>-12.03934293369645</v>
+        <v>-8.88155589724385</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.08797354695602</v>
       </c>
       <c r="E95">
-        <v>-37.50202294705976</v>
+        <v>-38.85874696704678</v>
       </c>
       <c r="F95">
-        <v>-6.73015353384867</v>
+        <v>-5.846314093736994</v>
       </c>
       <c r="G95">
-        <v>-11.15162345788642</v>
+        <v>-9.096526171836423</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.48463911464293</v>
       </c>
       <c r="E96">
-        <v>-41.11661920066418</v>
+        <v>-39.63639916601398</v>
       </c>
       <c r="F96">
-        <v>-6.910988208798309</v>
+        <v>-6.104195635004716</v>
       </c>
       <c r="G96">
-        <v>-11.17335718935173</v>
+        <v>-9.263579610293588</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.87197161902723</v>
       </c>
       <c r="E97">
-        <v>-41.94491106022215</v>
+        <v>-41.43622304646653</v>
       </c>
       <c r="F97">
-        <v>-6.525287092176415</v>
+        <v>-6.021988453950893</v>
       </c>
       <c r="G97">
-        <v>-11.08643219512709</v>
+        <v>-9.919388749986592</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.25407335489489</v>
       </c>
       <c r="E98">
-        <v>-44.13219344100798</v>
+        <v>-43.89361078791387</v>
       </c>
       <c r="F98">
-        <v>-7.226561812017704</v>
+        <v>-6.210052705408465</v>
       </c>
       <c r="G98">
-        <v>-12.48466096691151</v>
+        <v>-10.20343355725606</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.60836180253942</v>
       </c>
       <c r="E99">
-        <v>-46.58292885413805</v>
+        <v>-46.13832327606498</v>
       </c>
       <c r="F99">
-        <v>-7.372434412364787</v>
+        <v>-6.180271240543017</v>
       </c>
       <c r="G99">
-        <v>-13.13740123088961</v>
+        <v>-10.38740057287336</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.9407971246956</v>
       </c>
       <c r="E100">
-        <v>-47.5740963383299</v>
+        <v>-48.1973071955025</v>
       </c>
       <c r="F100">
-        <v>-8.064511354749094</v>
+        <v>-6.544499831533244</v>
       </c>
       <c r="G100">
-        <v>-13.55037523418599</v>
+        <v>-10.69860178520147</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.23165354140681</v>
       </c>
       <c r="E101">
-        <v>-49.03448844953752</v>
+        <v>-50.31923803576514</v>
       </c>
       <c r="F101">
-        <v>-7.551399462086308</v>
+        <v>-6.636868181333508</v>
       </c>
       <c r="G101">
-        <v>-13.99135479747184</v>
+        <v>-10.78933059625074</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.50877410567584</v>
       </c>
       <c r="E102">
-        <v>-51.30023456733576</v>
+        <v>-52.46852991598212</v>
       </c>
       <c r="F102">
-        <v>-7.820833000969771</v>
+        <v>-6.623361236647161</v>
       </c>
       <c r="G102">
-        <v>-13.0403128618594</v>
+        <v>-10.90698738471643</v>
       </c>
     </row>
   </sheetData>
